--- a/Articoli/Settimana fiscale/18 - Scomposizione ROE/Old/ScomposizioniROE2025_24.XLSX
+++ b/Articoli/Settimana fiscale/18 - Scomposizione ROE/Old/ScomposizioniROE2025_24.XLSX
@@ -28628,8 +28628,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010049B2E99503D3AD4DA2231F0D240043DD" ma:contentTypeVersion="19" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="22957244c50e327efd2a679e0bd8d1db">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="77a3f60d-3740-4b8f-aea2-18b203205ead" xmlns:ns3="6c014026-a0ef-45dc-9ca9-ac355db24e99" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e98c80d96d6165678046d3cbd7da068c" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010049B2E99503D3AD4DA2231F0D240043DD" ma:contentTypeVersion="19" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="5d22b860b2d7b05646517e191754a185">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="77a3f60d-3740-4b8f-aea2-18b203205ead" xmlns:ns3="6c014026-a0ef-45dc-9ca9-ac355db24e99" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c3ef981538194d0481c402a9a66d521d" ns2:_="" ns3:_="">
     <xsd:import namespace="77a3f60d-3740-4b8f-aea2-18b203205ead"/>
     <xsd:import namespace="6c014026-a0ef-45dc-9ca9-ac355db24e99"/>
     <xsd:element name="properties">
@@ -28908,22 +28908,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDD81876-7612-43AB-BBF3-AB26CEC6F57C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="77a3f60d-3740-4b8f-aea2-18b203205ead"/>
-    <ds:schemaRef ds:uri="6c014026-a0ef-45dc-9ca9-ac355db24e99"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{323BA2A1-C8E0-461F-B85E-849B8C8954CB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
